--- a/OUTSOURCING.xlsx
+++ b/OUTSOURCING.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="B1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,414 +492,6 @@
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>urlAtas</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>264</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>32746668000179-1-000026/2024-000001</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>32746668000179-1-000026/2024</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>00008</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2024-06-20</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Contratos.gov.br</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Contratação de empresa especializada em outsourcing de impressão com registro de preços para eventual locação de impressoras, incluindo suprimentos e manutenção, exceto papel, para a Sede, Regional e Escritórios Descentralizados, conforme condições, quantidades, exigências e estimativas estabelecidas neste instrumento e seus anexos.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>927487</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>CONSELHO REGIONAL DOS TECNICOS INDUSTRIAIS DA 4 REGIAO - CRT-04</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>CONSELHO REG. DOS TECNICOS INDUSTRIAIS 4ª-SC</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/pncp-api/v1/orgaos/32746668000179/compras/2024/000026/atas/000001/arquivos/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>71</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>00394452000103-1-014873/2023-000001</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>00394452000103-1-014873/2023</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>00119</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Contratos.gov.br</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Contratação de serviços de outsourcing de impressão, englobando o fornecimento de equipamentos, manutenção preventiva e corretiva dos equipamentos com substituição de peças, componentes e materiais utilizados na manutenção, e fornecimento de insumos originais, inclusive papel, e sistema de gerenciamento informatizado de impressões efetivamente realizadas.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>160218</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>COMANDO DO EXERCITO</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>COLÉGIO MILITAR DE BELÉM</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/pncp-api/v1/orgaos/00394452000103/compras/2023/014873/atas/000001/arquivos/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>55</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2024-06-03</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>00394452000103-1-006239/2024-000001</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00394452000103-1-006239/2024</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>00059</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2024-06-04</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Contratos.gov.br</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>O objeto da presente licitação é a contratação de serviço de impressão com fornecimento de insumos (exceto papel), peças, sistema de gerenciamento de impressões, treinamento dos usuários, suporte técnico e manutenção, por meio de outsourcing, com locação de equipamentos para funções de cópias, impressões e digitalização em prol do Hospital Militar de Área de São Paulo, conforme condições, quantidades e exigências estabelecidas no Edital e seus anexos.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>160495</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>COMANDO DO EXERCITO</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>HOSPITAL MILITAR DE ÁREA DE SÃO PAULO</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/pncp-api/v1/orgaos/00394452000103/compras/2024/006239/atas/000001/arquivos/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2024-06-03</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>10728444000100-1-000020/2024-000001</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>10728444000100-1-000020/2024</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>01101</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2024-06-03</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Contratos.gov.br</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Contratação de serviços continuados de outsourcing para operação de almoxarifado virtual, sob demanda, visando ao suprimento de materiais de consumo, por meio de ferramenta automatizada, a ser disponibilizada e suportada pela CONTRATADA em sua própria infraestrutura computacional ,que será acessada e operada pela CONTRATANTE, com o uso de browsers disponíveis no mercado, como MS Edge, Mozilla Firefox e Google Chrome.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>158134</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>INSTITUTO FEDERAL DE EDUCACAO, CIENCIA E TECNOLOGIA DE SERGIPE</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>INST.FED.DE EDUC.,CIENC.E TEC.DE SERGIPE</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/pncp-api/v1/orgaos/10728444000100/compras/2024/000020/atas/000001/arquivos/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>105</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>00394452000103-1-004876/2024-000001</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>00394452000103-1-004876/2024</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>03601</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Contratos.gov.br</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Contratação de serviço de outsourcing de impressão, para atender as necessidades do GCALC da Guarnição de João Pessoa.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>160175</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>COMANDO DO EXERCITO</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>ADMINISTRATIVA DA GUARNICÃO DE JOÃO PESSOA</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/pncp-api/v1/orgaos/00394452000103/compras/2024/004876/atas/000001/arquivos/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>116</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2024-05-27</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>00444232000139-1-000128/2024-000001</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>00444232000139-1-000128/2024</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>01014</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Contratos.gov.br</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>A contratação de empresa especializada na prestação de serviços de locação de impressoras e serviço de impressão (outsourcing), com fornecimento de equipamentos, sistema de gerenciamento de impressões efetivamente realizadas, manutenções preventivas e corretivas dos equipamentos com substituição de peças, componentes e materiais utilizados na manutenção e fornecimento de insumos, exceto papel e cartões em PVC (crachá), conforme o Termo de Referência anexo a este Edital.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>168008</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>INDUSTRIA DE MATERIAL BELICO DO BRASIL</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>INDUSTRIA DE MATERIAL BELICO DO BRASIL/FE</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/pncp-api/v1/orgaos/00444232000139/compras/2024/000128/atas/000001/arquivos/1</t>
         </is>
       </c>
     </row>
